--- a/NF.xlsx
+++ b/NF.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fnsul-my.sharepoint.com/personal/jungbin_lee_fnsusa_com/Documents/바탕 화면/code/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="101" documentId="8_{17F6C150-52D1-4709-B32B-2081CAA0F213}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9ED19F7D-E457-4FFC-B6E0-96009ACC880B}"/>
+  <xr:revisionPtr revIDLastSave="127" documentId="8_{17F6C150-52D1-4709-B32B-2081CAA0F213}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FCC2EC27-C78E-4A69-A878-B5A5C9396124}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{CE368B0D-5E19-4AE2-AF1A-E02F0281253F}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="76">
   <si>
     <t>NF1</t>
   </si>
@@ -258,6 +258,15 @@
   </si>
   <si>
     <t>LINE SET</t>
+  </si>
+  <si>
+    <t>NEW</t>
+  </si>
+  <si>
+    <t>nEW</t>
+  </si>
+  <si>
+    <t>New</t>
   </si>
 </sst>
 </file>
@@ -755,13 +764,17 @@
       <c r="A13" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="1"/>
+      <c r="B13" s="1">
+        <v>2661</v>
+      </c>
     </row>
     <row r="14" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="1"/>
+      <c r="B14" s="1" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="15" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A15" s="1" t="s">
@@ -799,7 +812,9 @@
       <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B19" s="1"/>
+      <c r="B19" s="1">
+        <v>2643</v>
+      </c>
     </row>
     <row r="20" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A20" s="1" t="s">
@@ -825,69 +840,75 @@
       <c r="A23" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="1">
-        <v>2643</v>
+      <c r="B23" s="1" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A24" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B24" s="1">
-        <v>2644</v>
-      </c>
+      <c r="B24" s="1"/>
     </row>
     <row r="25" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A25" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B25" s="1"/>
+      <c r="B25" s="1">
+        <v>2644</v>
+      </c>
     </row>
     <row r="26" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A26" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B26" s="1"/>
+      <c r="B26" s="1" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="27" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A27" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B27" s="1"/>
+      <c r="B27" s="1">
+        <v>2657</v>
+      </c>
     </row>
     <row r="28" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A28" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B28" s="1"/>
+      <c r="B28" s="1">
+        <v>2658</v>
+      </c>
     </row>
     <row r="29" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A29" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B29" s="1"/>
+      <c r="B29" s="1">
+        <v>2659</v>
+      </c>
     </row>
     <row r="30" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A30" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B30" s="1"/>
+      <c r="B30" s="1">
+        <v>2660</v>
+      </c>
     </row>
     <row r="31" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A31" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B31" s="1">
-        <v>2618</v>
-      </c>
+      <c r="B31" s="1"/>
     </row>
     <row r="32" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A32" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B32" s="1">
-        <v>2617</v>
-      </c>
+      <c r="B32" s="1"/>
     </row>
     <row r="33" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A33" s="1" t="s">
@@ -933,17 +954,13 @@
       <c r="A39" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B39" s="1">
-        <v>2619</v>
-      </c>
+      <c r="B39" s="1"/>
     </row>
     <row r="40" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A40" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B40" s="1">
-        <v>2620</v>
-      </c>
+      <c r="B40" s="1"/>
     </row>
     <row r="41" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A41" s="1" t="s">
@@ -981,7 +998,9 @@
       <c r="A46" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B46" s="1"/>
+      <c r="B46" s="1">
+        <v>2654</v>
+      </c>
     </row>
     <row r="47" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A47" s="1" t="s">
@@ -1022,7 +1041,9 @@
       <c r="A52" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B52" s="1"/>
+      <c r="B52" s="1">
+        <v>2656</v>
+      </c>
     </row>
     <row r="53" spans="1:3" ht="20" x14ac:dyDescent="0.4">
       <c r="A53" s="1" t="s">
@@ -1052,19 +1073,25 @@
       <c r="A57" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B57" s="1"/>
+      <c r="B57" s="1" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="58" spans="1:3" ht="20" x14ac:dyDescent="0.4">
       <c r="A58" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B58" s="1"/>
+      <c r="B58" s="1" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="59" spans="1:3" ht="20" x14ac:dyDescent="0.4">
       <c r="A59" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B59" s="1"/>
+      <c r="B59" s="1" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="60" spans="1:3" ht="20" x14ac:dyDescent="0.4">
       <c r="A60" s="1" t="s">
@@ -1096,13 +1123,13 @@
       </c>
       <c r="B64" s="1"/>
     </row>
-    <row r="65" spans="1:2" ht="20" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:3" ht="20" x14ac:dyDescent="0.4">
       <c r="A65" s="1" t="s">
         <v>41</v>
       </c>
       <c r="B65" s="1"/>
     </row>
-    <row r="66" spans="1:2" ht="20" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:3" ht="20" x14ac:dyDescent="0.4">
       <c r="A66" s="1" t="s">
         <v>43</v>
       </c>
@@ -1110,27 +1137,30 @@
         <v>2631</v>
       </c>
     </row>
-    <row r="67" spans="1:2" ht="20" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:3" ht="20" x14ac:dyDescent="0.4">
       <c r="A67" s="1" t="s">
         <v>45</v>
       </c>
       <c r="B67" s="1"/>
     </row>
-    <row r="68" spans="1:2" ht="20" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:3" ht="20" x14ac:dyDescent="0.4">
       <c r="A68" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B68" s="1">
-        <v>2609</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" ht="20" x14ac:dyDescent="0.4">
+      <c r="B68" s="1"/>
+    </row>
+    <row r="69" spans="1:3" ht="20" x14ac:dyDescent="0.4">
       <c r="A69" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B69" s="1"/>
-    </row>
-    <row r="70" spans="1:2" ht="20" x14ac:dyDescent="0.4">
+      <c r="B69" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" ht="20" x14ac:dyDescent="0.4">
       <c r="A70" s="3" t="s">
         <v>71</v>
       </c>

--- a/NF.xlsx
+++ b/NF.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fnsul-my.sharepoint.com/personal/jungbin_lee_fnsusa_com/Documents/바탕 화면/code/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="127" documentId="8_{17F6C150-52D1-4709-B32B-2081CAA0F213}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FCC2EC27-C78E-4A69-A878-B5A5C9396124}"/>
+  <xr:revisionPtr revIDLastSave="159" documentId="8_{17F6C150-52D1-4709-B32B-2081CAA0F213}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{467C4879-D32A-452B-BE51-89ECCB408F6F}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{CE368B0D-5E19-4AE2-AF1A-E02F0281253F}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="74">
   <si>
     <t>NF1</t>
   </si>
@@ -260,13 +260,7 @@
     <t>LINE SET</t>
   </si>
   <si>
-    <t>NEW</t>
-  </si>
-  <si>
-    <t>nEW</t>
-  </si>
-  <si>
-    <t>New</t>
+    <t>new</t>
   </si>
 </sst>
 </file>
@@ -326,7 +320,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -335,6 +329,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -676,9 +673,9 @@
   <dimension ref="A1:D70"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9" style="2" customWidth="1"/>
-    <col min="2" max="2" width="17.25" style="2" customWidth="1"/>
-    <col min="3" max="3" width="9.83203125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="9" style="4" customWidth="1"/>
+    <col min="2" max="2" width="17.25" style="4" customWidth="1"/>
+    <col min="3" max="3" width="9.83203125" style="4" customWidth="1"/>
     <col min="4" max="4" width="19.08203125" style="2" customWidth="1"/>
   </cols>
   <sheetData>
@@ -764,25 +761,19 @@
       <c r="A13" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="1">
-        <v>2661</v>
-      </c>
+      <c r="B13" s="1"/>
     </row>
     <row r="14" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>73</v>
-      </c>
+      <c r="B14" s="1"/>
     </row>
     <row r="15" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A15" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="1">
-        <v>2638</v>
-      </c>
+      <c r="B15" s="1"/>
     </row>
     <row r="16" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A16" s="1" t="s">
@@ -840,9 +831,7 @@
       <c r="A23" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>73</v>
-      </c>
+      <c r="B23" s="1"/>
     </row>
     <row r="24" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A24" s="1" t="s">
@@ -862,41 +851,35 @@
       <c r="A26" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>73</v>
-      </c>
+      <c r="B26" s="1"/>
     </row>
     <row r="27" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A27" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B27" s="1">
-        <v>2657</v>
+      <c r="B27" s="1" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A28" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B28" s="1">
-        <v>2658</v>
+      <c r="B28" s="1" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A29" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B29" s="1">
-        <v>2659</v>
-      </c>
+      <c r="B29" s="1"/>
     </row>
     <row r="30" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A30" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B30" s="1">
-        <v>2660</v>
-      </c>
+      <c r="B30" s="1"/>
     </row>
     <row r="31" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A31" s="1" t="s">
@@ -927,14 +910,16 @@
         <v>58</v>
       </c>
       <c r="B35" s="1">
-        <v>2623</v>
+        <v>2674</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A36" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B36" s="1"/>
+      <c r="B36" s="1">
+        <v>2672</v>
+      </c>
     </row>
     <row r="37" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A37" s="1" t="s">
@@ -948,7 +933,9 @@
       <c r="A38" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B38" s="1"/>
+      <c r="B38" s="1">
+        <v>2671</v>
+      </c>
     </row>
     <row r="39" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A39" s="1" t="s">
@@ -991,7 +978,7 @@
         <v>1</v>
       </c>
       <c r="B45" s="1">
-        <v>2621</v>
+        <v>2654</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="20" x14ac:dyDescent="0.4">
@@ -999,7 +986,7 @@
         <v>3</v>
       </c>
       <c r="B46" s="1">
-        <v>2654</v>
+        <v>2673</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="20" x14ac:dyDescent="0.4">
@@ -1033,7 +1020,7 @@
       <c r="B51" s="1">
         <v>2535</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="C51" s="4" t="s">
         <v>69</v>
       </c>
     </row>
@@ -1073,25 +1060,19 @@
       <c r="A57" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B57" s="1" t="s">
-        <v>73</v>
-      </c>
+      <c r="B57" s="1"/>
     </row>
     <row r="58" spans="1:3" ht="20" x14ac:dyDescent="0.4">
       <c r="A58" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B58" s="1" t="s">
-        <v>73</v>
-      </c>
+      <c r="B58" s="1"/>
     </row>
     <row r="59" spans="1:3" ht="20" x14ac:dyDescent="0.4">
       <c r="A59" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B59" s="1" t="s">
-        <v>73</v>
-      </c>
+      <c r="B59" s="1"/>
     </row>
     <row r="60" spans="1:3" ht="20" x14ac:dyDescent="0.4">
       <c r="A60" s="1" t="s">
@@ -1115,26 +1096,32 @@
       <c r="A63" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B63" s="1"/>
+      <c r="B63" s="1" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="64" spans="1:3" ht="20" x14ac:dyDescent="0.4">
       <c r="A64" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B64" s="1"/>
+      <c r="B64" s="1" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="65" spans="1:3" ht="20" x14ac:dyDescent="0.4">
       <c r="A65" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B65" s="1"/>
+      <c r="B65" s="1">
+        <v>2631</v>
+      </c>
     </row>
     <row r="66" spans="1:3" ht="20" x14ac:dyDescent="0.4">
       <c r="A66" s="1" t="s">
         <v>43</v>
       </c>
       <c r="B66" s="1">
-        <v>2631</v>
+        <v>2535</v>
       </c>
     </row>
     <row r="67" spans="1:3" ht="20" x14ac:dyDescent="0.4">
@@ -1153,11 +1140,9 @@
       <c r="A69" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B69" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>75</v>
+      <c r="B69" s="1"/>
+      <c r="C69" s="4">
+        <v>2666</v>
       </c>
     </row>
     <row r="70" spans="1:3" ht="20" x14ac:dyDescent="0.4">

--- a/NF.xlsx
+++ b/NF.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fnsul-my.sharepoint.com/personal/jungbin_lee_fnsusa_com/Documents/바탕 화면/code/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="159" documentId="8_{17F6C150-52D1-4709-B32B-2081CAA0F213}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{467C4879-D32A-452B-BE51-89ECCB408F6F}"/>
+  <xr:revisionPtr revIDLastSave="204" documentId="8_{17F6C150-52D1-4709-B32B-2081CAA0F213}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5FB23961-B39E-4BF6-9E2C-B090A3937297}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{CE368B0D-5E19-4AE2-AF1A-E02F0281253F}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="79">
   <si>
     <t>NF1</t>
   </si>
@@ -248,9 +248,6 @@
     <t>NF44</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
     <t>DOC1</t>
   </si>
   <si>
@@ -261,13 +258,31 @@
   </si>
   <si>
     <t>new</t>
+  </si>
+  <si>
+    <t>71001_1G</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>NF69</t>
+  </si>
+  <si>
+    <t>NF70</t>
+  </si>
+  <si>
+    <t>NF71</t>
+  </si>
+  <si>
+    <t>NF72</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -279,6 +294,13 @@
     <font>
       <sz val="16"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="129"/>
@@ -320,7 +342,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -330,6 +352,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -670,7 +695,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8883645C-3432-47A1-B329-9577D994FDF6}">
-  <dimension ref="A1:D70"/>
+  <dimension ref="A1:D74"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="4" customWidth="1"/>
@@ -691,7 +716,9 @@
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="1"/>
+      <c r="B2" s="1" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="3" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
@@ -721,17 +748,13 @@
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>72</v>
-      </c>
+      <c r="B7" s="1"/>
     </row>
     <row r="8" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="1">
-        <v>2616</v>
-      </c>
+      <c r="B8" s="1"/>
     </row>
     <row r="9" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
@@ -743,44 +766,56 @@
       <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="1"/>
+      <c r="B10" s="1">
+        <v>2720</v>
+      </c>
     </row>
     <row r="11" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="1"/>
+      <c r="B11" s="1">
+        <v>2724</v>
+      </c>
     </row>
     <row r="12" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="1"/>
+      <c r="B12" s="1" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="13" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="1"/>
+      <c r="B13" s="1">
+        <v>2750</v>
+      </c>
     </row>
     <row r="14" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="1"/>
+      <c r="B14" s="1">
+        <v>2751</v>
+      </c>
     </row>
     <row r="15" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A15" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="1"/>
+      <c r="B15" s="1">
+        <v>2752</v>
+      </c>
     </row>
     <row r="16" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A16" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B16" s="1">
-        <v>2642</v>
+        <v>2753</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="20" x14ac:dyDescent="0.4">
@@ -788,7 +823,7 @@
         <v>32</v>
       </c>
       <c r="B17" s="1">
-        <v>2639</v>
+        <v>2754</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="20" x14ac:dyDescent="0.4">
@@ -796,24 +831,20 @@
         <v>34</v>
       </c>
       <c r="B18" s="1">
-        <v>2640</v>
+        <v>2755</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B19" s="1">
-        <v>2643</v>
-      </c>
+      <c r="B19" s="1"/>
     </row>
     <row r="20" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A20" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="1">
-        <v>2641</v>
-      </c>
+      <c r="B20" s="1"/>
     </row>
     <row r="21" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A21" s="1" t="s">
@@ -825,13 +856,17 @@
       <c r="A22" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="1"/>
+      <c r="B22" s="1">
+        <v>2749</v>
+      </c>
     </row>
     <row r="23" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A23" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="1"/>
+      <c r="B23" s="1">
+        <v>2719</v>
+      </c>
     </row>
     <row r="24" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A24" s="1" t="s">
@@ -843,9 +878,7 @@
       <c r="A25" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B25" s="1">
-        <v>2644</v>
-      </c>
+      <c r="B25" s="1"/>
     </row>
     <row r="26" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A26" s="1" t="s">
@@ -857,8 +890,8 @@
       <c r="A27" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>73</v>
+      <c r="B27" s="1">
+        <v>2745</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="20" x14ac:dyDescent="0.4">
@@ -866,7 +899,7 @@
         <v>51</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="20" x14ac:dyDescent="0.4">
@@ -897,28 +930,30 @@
       <c r="A33" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B33" s="1"/>
+      <c r="B33" s="1" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="34" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A34" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B34" s="1"/>
+      <c r="B34" s="5" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="35" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A35" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B35" s="1">
-        <v>2674</v>
-      </c>
+      <c r="B35" s="1"/>
     </row>
     <row r="36" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A36" s="1" t="s">
         <v>59</v>
       </c>
       <c r="B36" s="1">
-        <v>2672</v>
+        <v>2757</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="20" x14ac:dyDescent="0.4">
@@ -934,14 +969,16 @@
         <v>62</v>
       </c>
       <c r="B38" s="1">
-        <v>2671</v>
+        <v>2758</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A39" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B39" s="1"/>
+      <c r="B39" s="1" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="40" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A40" s="1" t="s">
@@ -977,17 +1014,13 @@
       <c r="A45" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B45" s="1">
-        <v>2654</v>
-      </c>
+      <c r="B45" s="1"/>
     </row>
     <row r="46" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A46" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B46" s="1">
-        <v>2673</v>
-      </c>
+      <c r="B46" s="1"/>
     </row>
     <row r="47" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A47" s="1" t="s">
@@ -1001,157 +1034,192 @@
       </c>
       <c r="B48" s="1"/>
     </row>
-    <row r="49" spans="1:3" ht="20" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A49" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B49" s="1"/>
     </row>
-    <row r="50" spans="1:3" ht="20" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A50" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B50" s="1"/>
     </row>
-    <row r="51" spans="1:3" ht="20" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A51" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B51" s="1">
-        <v>2535</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" ht="20" x14ac:dyDescent="0.4">
+      <c r="B51" s="1"/>
+    </row>
+    <row r="52" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A52" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B52" s="1">
-        <v>2656</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" ht="20" x14ac:dyDescent="0.4">
+        <v>2726</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A53" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B53" s="1"/>
     </row>
-    <row r="54" spans="1:3" ht="20" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A54" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B54" s="1"/>
     </row>
-    <row r="55" spans="1:3" ht="20" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A55" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B55" s="1"/>
     </row>
-    <row r="56" spans="1:3" ht="20" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A56" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B56" s="1"/>
     </row>
-    <row r="57" spans="1:3" ht="20" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A57" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B57" s="1"/>
-    </row>
-    <row r="58" spans="1:3" ht="20" x14ac:dyDescent="0.4">
+      <c r="B57" s="1">
+        <v>2783</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A58" s="1" t="s">
         <v>27</v>
       </c>
       <c r="B58" s="1"/>
     </row>
-    <row r="59" spans="1:3" ht="20" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A59" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B59" s="1"/>
-    </row>
-    <row r="60" spans="1:3" ht="20" x14ac:dyDescent="0.4">
+      <c r="B59" s="1">
+        <v>2781</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A60" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B60" s="1"/>
-    </row>
-    <row r="61" spans="1:3" ht="20" x14ac:dyDescent="0.4">
+      <c r="B60" s="1">
+        <v>2782</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A61" s="1" t="s">
         <v>33</v>
       </c>
       <c r="B61" s="1"/>
     </row>
-    <row r="62" spans="1:3" ht="20" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A62" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B62" s="1"/>
     </row>
-    <row r="63" spans="1:3" ht="20" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A63" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B63" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" ht="20" x14ac:dyDescent="0.4">
+      <c r="B63" s="1">
+        <v>2779</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A64" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B64" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" ht="20" x14ac:dyDescent="0.4">
+      <c r="B64" s="1">
+        <v>2780</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A65" s="1" t="s">
         <v>41</v>
       </c>
       <c r="B65" s="1">
-        <v>2631</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" ht="20" x14ac:dyDescent="0.4">
+        <v>2777</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A66" s="1" t="s">
         <v>43</v>
       </c>
       <c r="B66" s="1">
-        <v>2535</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" ht="20" x14ac:dyDescent="0.4">
+        <v>2778</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A67" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B67" s="1"/>
-    </row>
-    <row r="68" spans="1:3" ht="20" x14ac:dyDescent="0.4">
+      <c r="B67" s="1">
+        <v>2775</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" ht="20" x14ac:dyDescent="0.4">
       <c r="A68" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B68" s="1"/>
-    </row>
-    <row r="69" spans="1:3" ht="20" x14ac:dyDescent="0.4">
-      <c r="A69" s="3" t="s">
+      <c r="B68" s="1">
+        <v>2776</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" ht="20" x14ac:dyDescent="0.4">
+      <c r="A69" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B69" s="1">
+        <v>2773</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" ht="20" x14ac:dyDescent="0.4">
+      <c r="A70" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B70" s="1">
+        <v>2774</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" ht="20" x14ac:dyDescent="0.4">
+      <c r="A71" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B71" s="1">
+        <v>2535</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" ht="20" x14ac:dyDescent="0.4">
+      <c r="A72" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B72" s="1">
+        <v>2725</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" ht="20" x14ac:dyDescent="0.4">
+      <c r="A73" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B73" s="1"/>
+    </row>
+    <row r="74" spans="1:2" ht="20" x14ac:dyDescent="0.4">
+      <c r="A74" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B69" s="1"/>
-      <c r="C69" s="4">
-        <v>2666</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" ht="20" x14ac:dyDescent="0.4">
-      <c r="A70" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B70" s="1"/>
+      <c r="B74" s="1"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
